--- a/assets/database/Rifa.xlsx
+++ b/assets/database/Rifa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10" count="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10" count="9">
   <si>
     <t>Numeros comprados</t>
   </si>
@@ -50,27 +50,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <fonts count="9">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -92,6 +72,11 @@
     <font>
       <sz val="11"/>
       <color rgb="FF2B579A"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="0"/>
     </font>
@@ -145,30 +130,30 @@
   </borders>
   <cellStyleXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -270,8 +255,11 @@
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9"/>
-    </row>
+      <c r="A9">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11"/>
     <row r="12"/>
     <row r="17"/>

--- a/assets/database/Rifa.xlsx
+++ b/assets/database/Rifa.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\AsociacionAlmasBellas\assets\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\asociacionalmasbellas-web\assets\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Numeros comprados</t>
   </si>
@@ -37,13 +37,17 @@
   </si>
   <si>
     <t>Descripcion premio</t>
+  </si>
+  <si>
+    <t>Esta rifa financiará la rehabilitación de Vida para que pueda volver a andar.
+El premio son unos juguetes variados para perros junto con llaveros</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -55,6 +59,11 @@
       <color rgb="FF2B579A"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -64,10 +73,7 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="64"/>
-        <bgColor indexed="65"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -77,45 +83,65 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color rgb="FF2B579A"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF2B579A"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="ConditionalFormatStyle" xfId="1"/>
     <cellStyle name="HeaderStyle" xfId="2"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -150,7 +176,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -185,7 +211,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -247,7 +273,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -271,11 +296,10 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -284,13 +308,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -366,7 +390,6 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -386,24 +409,26 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.42578" customWidth="1"/>
-    <col min="2" max="2" width="23.85547" customWidth="1"/>
-    <col min="3" max="3" width="18.28516" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="42.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -414,7 +439,10 @@
         <v>250</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>52</v>
+      </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
@@ -425,17 +453,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>85</v>
+      </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>5</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>